--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -2159,10 +2159,10 @@
         <v>40</v>
       </c>
       <c r="T10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="U10" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -1062,7 +1062,7 @@
         <v>676.5</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K4" t="n">
         <v>12</v>
@@ -1089,13 +1089,13 @@
         <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T4" t="n">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="U4" t="n">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1163,6 +1163,7 @@
 Tjäder
 Torta
 Orre
+Vanlig groda
 Fläcknycklar
 Revlummer</t>
         </is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -883,10 +883,10 @@
         <v>76</v>
       </c>
       <c r="T3" t="n">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="U3" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>

--- a/Översikt.xlsx
+++ b/Översikt.xlsx
@@ -621,7 +621,7 @@
         <v>46223</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
         <v>46223</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
         <v>46223</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46223</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>46223</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>46223</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>46223</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46223</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>46223</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         <v>46223</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>46223</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>46223</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>46223</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46223</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46223</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3229,7 +3229,7 @@
         <v>46223</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         <v>46223</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46223</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>46223</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>46223</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>46223</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>46223</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>46223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>46223</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>46223</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>46223</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>46223</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         <v>46223</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>46223</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46223</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46223</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>46223</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
